--- a/nr-cleaning/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:04:54+00:00</t>
+    <t>2024-03-06T15:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-cleaning/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:16:55+00:00</t>
+    <t>2024-03-06T15:26:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-cleaning/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:26:05+00:00</t>
+    <t>2024-03-06T16:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,7 +431,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/type-systeme-information-vs</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-systeme-information</t>
   </si>
   <si>
     <t>base64Binary
